--- a/Code and data/Initial data/Non sector data/DIVERS-HHI.xlsx
+++ b/Code and data/Initial data/Non sector data/DIVERS-HHI.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L233"/>
+  <dimension ref="A1:L238"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -448,7 +448,7 @@
         </is>
       </c>
       <c r="K2">
-        <v>0.153944</v>
+        <v>0.121529</v>
       </c>
     </row>
     <row r="3">
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="K3">
-        <v>0.150312</v>
+        <v>0.137468</v>
       </c>
     </row>
     <row r="4">
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="K4">
-        <v>0.15629</v>
+        <v>0.122471</v>
       </c>
     </row>
     <row r="5">
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="K5">
-        <v>0.173608</v>
+        <v>0.155148</v>
       </c>
     </row>
     <row r="6">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="K6">
-        <v>0.196683</v>
+        <v>0.138486</v>
       </c>
     </row>
     <row r="7">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="K7">
-        <v>0.192136</v>
+        <v>0.14705</v>
       </c>
     </row>
     <row r="8">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="K8">
-        <v>0.169881</v>
+        <v>0.134785</v>
       </c>
     </row>
     <row r="9">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="K9">
-        <v>0.140783</v>
+        <v>0.138331</v>
       </c>
     </row>
     <row r="10">
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="K10">
-        <v>0.25947</v>
+        <v>0.191838</v>
       </c>
     </row>
     <row r="11">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="K11">
-        <v>0.188605</v>
+        <v>0.140125</v>
       </c>
     </row>
     <row r="12">
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="K12">
-        <v>0.124165</v>
+        <v>0.133513</v>
       </c>
     </row>
     <row r="13">
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="K13">
-        <v>0.178681</v>
+        <v>0.139067</v>
       </c>
     </row>
     <row r="14">
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="K14">
-        <v>0.161842</v>
+        <v>0.121817</v>
       </c>
     </row>
     <row r="15">
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="K15">
-        <v>0.184566</v>
+        <v>0.167608</v>
       </c>
     </row>
     <row r="16">
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="K16">
-        <v>0.165506</v>
+        <v>0.144017</v>
       </c>
     </row>
     <row r="17">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="K17">
-        <v>0.33623</v>
+        <v>0.42393</v>
       </c>
     </row>
     <row r="18">
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="K18">
-        <v>0.109552</v>
+        <v>0.131302</v>
       </c>
     </row>
     <row r="19">
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="K19">
-        <v>0.162053</v>
+        <v>0.149566</v>
       </c>
     </row>
     <row r="20">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="K20">
-        <v>0.226431</v>
+        <v>0.165223</v>
       </c>
     </row>
     <row r="21">
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="K21">
-        <v>0.172203</v>
+        <v>0.152519</v>
       </c>
     </row>
     <row r="22">
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="K22">
-        <v>0.166093</v>
+        <v>0.13576</v>
       </c>
     </row>
     <row r="23">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="K23">
-        <v>0.163225</v>
+        <v>0.138531</v>
       </c>
     </row>
     <row r="24">
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="K24">
-        <v>0.12826</v>
+        <v>0.118754</v>
       </c>
     </row>
     <row r="25">
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="K25">
-        <v>0.224243</v>
+        <v>0.164345</v>
       </c>
     </row>
     <row r="26">
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="K26">
-        <v>0.12819</v>
+        <v>0.12117</v>
       </c>
     </row>
     <row r="27">
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="K27">
-        <v>0.147678</v>
+        <v>0.123494</v>
       </c>
     </row>
     <row r="28">
@@ -1358,7 +1358,7 @@
         </is>
       </c>
       <c r="K28">
-        <v>0.225283</v>
+        <v>0.227329</v>
       </c>
     </row>
     <row r="29">
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="K29">
-        <v>0.149114</v>
+        <v>0.126587</v>
       </c>
     </row>
     <row r="30">
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="K30">
-        <v>0.282616</v>
+        <v>0.167656</v>
       </c>
     </row>
     <row r="31">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="K31">
-        <v>0.246918</v>
+        <v>0.150895</v>
       </c>
     </row>
     <row r="32">
@@ -1498,7 +1498,7 @@
         </is>
       </c>
       <c r="K32">
-        <v>0.178173</v>
+        <v>0.124235</v>
       </c>
     </row>
     <row r="33">
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="K33">
-        <v>0.237802</v>
+        <v>0.143447</v>
       </c>
     </row>
     <row r="34">
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="K34">
-        <v>0.196429</v>
+        <v>0.15095</v>
       </c>
     </row>
     <row r="35">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="K35">
-        <v>0.191979</v>
+        <v>0.152971</v>
       </c>
     </row>
     <row r="36">
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="K36">
-        <v>0.22806</v>
+        <v>0.139886</v>
       </c>
     </row>
     <row r="37">
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="K37">
-        <v>0.41527</v>
+        <v>0.227259</v>
       </c>
     </row>
     <row r="38">
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="K38">
-        <v>0.24314</v>
+        <v>0.159238</v>
       </c>
     </row>
     <row r="39">
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="K39">
-        <v>0.234511</v>
+        <v>0.205857</v>
       </c>
     </row>
     <row r="40">
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="K40">
-        <v>0.27745</v>
+        <v>0.197076</v>
       </c>
     </row>
     <row r="41">
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="K41">
-        <v>0.254609</v>
+        <v>0.160635</v>
       </c>
     </row>
     <row r="42">
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="K42">
-        <v>0.311229</v>
+        <v>0.172019</v>
       </c>
     </row>
     <row r="43">
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="K43">
-        <v>0.222032</v>
+        <v>0.163687</v>
       </c>
     </row>
     <row r="44">
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c r="K44">
-        <v>0.1816</v>
+        <v>0.143652</v>
       </c>
     </row>
     <row r="45">
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="K45">
-        <v>0.200173</v>
+        <v>0.161712</v>
       </c>
     </row>
     <row r="46">
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="K46">
-        <v>0.24799</v>
+        <v>0.167538</v>
       </c>
     </row>
     <row r="47">
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="K47">
-        <v>0.270536</v>
+        <v>0.181217</v>
       </c>
     </row>
     <row r="48">
@@ -2058,7 +2058,7 @@
         </is>
       </c>
       <c r="K48">
-        <v>0.169567</v>
+        <v>0.147</v>
       </c>
     </row>
     <row r="49">
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="K49">
-        <v>0.172958</v>
+        <v>0.120819</v>
       </c>
     </row>
     <row r="50">
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="K50">
-        <v>0.349396</v>
+        <v>0.218469</v>
       </c>
     </row>
     <row r="51">
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="K51">
-        <v>0.237919</v>
+        <v>0.177181</v>
       </c>
     </row>
     <row r="52">
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="K52">
-        <v>0.157207</v>
+        <v>0.123155</v>
       </c>
     </row>
     <row r="53">
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="K53">
-        <v>0.179926</v>
+        <v>0.181638</v>
       </c>
     </row>
     <row r="54">
@@ -2268,7 +2268,7 @@
         </is>
       </c>
       <c r="K54">
-        <v>0.233764</v>
+        <v>0.139977</v>
       </c>
     </row>
     <row r="55">
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="K55">
-        <v>0.197048</v>
+        <v>0.162695</v>
       </c>
     </row>
     <row r="56">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="K56">
-        <v>0.368476</v>
+        <v>0.250938</v>
       </c>
     </row>
     <row r="57">
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="K57">
-        <v>0.190623</v>
+        <v>0.125818</v>
       </c>
     </row>
     <row r="58">
@@ -2408,7 +2408,7 @@
         </is>
       </c>
       <c r="K58">
-        <v>0.199367</v>
+        <v>0.163333</v>
       </c>
     </row>
     <row r="59">
@@ -2443,7 +2443,7 @@
         </is>
       </c>
       <c r="K59">
-        <v>0.228224</v>
+        <v>0.159676</v>
       </c>
     </row>
     <row r="60">
@@ -2478,7 +2478,7 @@
         </is>
       </c>
       <c r="K60">
-        <v>0.183941</v>
+        <v>0.151576</v>
       </c>
     </row>
     <row r="61">
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="K61">
-        <v>0.16895</v>
+        <v>0.124953</v>
       </c>
     </row>
     <row r="62">
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="K62">
-        <v>0.179745</v>
+        <v>0.150556</v>
       </c>
     </row>
     <row r="63">
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="K63">
-        <v>0.18205</v>
+        <v>0.153534</v>
       </c>
     </row>
     <row r="64">
@@ -2618,7 +2618,7 @@
         </is>
       </c>
       <c r="K64">
-        <v>0.250291</v>
+        <v>0.210853</v>
       </c>
     </row>
     <row r="65">
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="K65">
-        <v>0.204447</v>
+        <v>0.163591</v>
       </c>
     </row>
     <row r="66">
@@ -2688,7 +2688,7 @@
         </is>
       </c>
       <c r="K66">
-        <v>0.178044</v>
+        <v>0.176851</v>
       </c>
     </row>
     <row r="67">
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="K67">
-        <v>0.182856</v>
+        <v>0.144857</v>
       </c>
     </row>
     <row r="68">
@@ -2758,7 +2758,7 @@
         </is>
       </c>
       <c r="K68">
-        <v>0.280692</v>
+        <v>0.169338</v>
       </c>
     </row>
     <row r="69">
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="K69">
-        <v>0.174693</v>
+        <v>0.138103</v>
       </c>
     </row>
     <row r="70">
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="K70">
-        <v>0.286299</v>
+        <v>0.16958</v>
       </c>
     </row>
     <row r="71">
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="K71">
-        <v>0.21635</v>
+        <v>0.134341</v>
       </c>
     </row>
     <row r="72">
@@ -2898,7 +2898,7 @@
         </is>
       </c>
       <c r="K72">
-        <v>0.152337</v>
+        <v>0.132073</v>
       </c>
     </row>
     <row r="73">
@@ -2933,7 +2933,7 @@
         </is>
       </c>
       <c r="K73">
-        <v>0.185656</v>
+        <v>0.13725</v>
       </c>
     </row>
     <row r="74">
@@ -2968,7 +2968,7 @@
         </is>
       </c>
       <c r="K74">
-        <v>0.181432</v>
+        <v>0.14312</v>
       </c>
     </row>
     <row r="75">
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="K75">
-        <v>0.202737</v>
+        <v>0.200622</v>
       </c>
     </row>
     <row r="76">
@@ -3038,7 +3038,7 @@
         </is>
       </c>
       <c r="K76">
-        <v>0.168479</v>
+        <v>0.162131</v>
       </c>
     </row>
     <row r="77">
@@ -3073,7 +3073,7 @@
         </is>
       </c>
       <c r="K77">
-        <v>0.207781</v>
+        <v>0.191187</v>
       </c>
     </row>
     <row r="78">
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="K78">
-        <v>0.234632</v>
+        <v>0.215689</v>
       </c>
     </row>
     <row r="79">
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="K79">
-        <v>0.209994</v>
+        <v>0.188896</v>
       </c>
     </row>
     <row r="80">
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="K80">
-        <v>0.144041</v>
+        <v>0.130707</v>
       </c>
     </row>
     <row r="81">
@@ -3213,7 +3213,7 @@
         </is>
       </c>
       <c r="K81">
-        <v>0.145586</v>
+        <v>0.141031</v>
       </c>
     </row>
     <row r="82">
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="K82">
-        <v>0.112236</v>
+        <v>0.387697</v>
       </c>
     </row>
     <row r="83">
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="K83">
-        <v>0.103743</v>
+        <v>0.506915</v>
       </c>
     </row>
     <row r="84">
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="K84">
-        <v>0.266551</v>
+        <v>0.253826</v>
       </c>
     </row>
     <row r="85">
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="K85">
-        <v>0.252</v>
+        <v>0.242592</v>
       </c>
     </row>
     <row r="86">
@@ -3388,7 +3388,7 @@
         </is>
       </c>
       <c r="K86">
-        <v>0.236013</v>
+        <v>0.230201</v>
       </c>
     </row>
     <row r="87">
@@ -3423,7 +3423,7 @@
         </is>
       </c>
       <c r="K87">
-        <v>0.258118</v>
+        <v>0.234657</v>
       </c>
     </row>
     <row r="88">
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="K88">
-        <v>0.523182</v>
+        <v>0.493784</v>
       </c>
     </row>
     <row r="89">
@@ -3493,7 +3493,7 @@
         </is>
       </c>
       <c r="K89">
-        <v>0.302216</v>
+        <v>0.297859</v>
       </c>
     </row>
     <row r="90">
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="K90">
-        <v>0.112236</v>
+        <v>0.241358</v>
       </c>
     </row>
     <row r="91">
@@ -3563,7 +3563,7 @@
         </is>
       </c>
       <c r="K91">
-        <v>0.329327</v>
+        <v>0.320083</v>
       </c>
     </row>
     <row r="92">
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="K92">
-        <v>0.186911</v>
+        <v>0.183064</v>
       </c>
     </row>
     <row r="93">
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="K93">
-        <v>0.326066</v>
+        <v>0.338042</v>
       </c>
     </row>
     <row r="94">
@@ -3668,7 +3668,7 @@
         </is>
       </c>
       <c r="K94">
-        <v>0.199351</v>
+        <v>0.152454</v>
       </c>
     </row>
     <row r="95">
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="K95">
-        <v>0.185518</v>
+        <v>0.156479</v>
       </c>
     </row>
     <row r="96">
@@ -3738,7 +3738,7 @@
         </is>
       </c>
       <c r="K96">
-        <v>0.192903</v>
+        <v>0.133851</v>
       </c>
     </row>
     <row r="97">
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="K97">
-        <v>0.255908</v>
+        <v>0.172947</v>
       </c>
     </row>
     <row r="98">
@@ -3808,7 +3808,7 @@
         </is>
       </c>
       <c r="K98">
-        <v>0.233687</v>
+        <v>0.15642</v>
       </c>
     </row>
     <row r="99">
@@ -3843,7 +3843,7 @@
         </is>
       </c>
       <c r="K99">
-        <v>0.197499</v>
+        <v>0.163787</v>
       </c>
     </row>
     <row r="100">
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="K100">
-        <v>0.19287</v>
+        <v>0.131812</v>
       </c>
     </row>
     <row r="101">
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="K101">
-        <v>0.160215</v>
+        <v>0.120485</v>
       </c>
     </row>
     <row r="102">
@@ -3948,7 +3948,7 @@
         </is>
       </c>
       <c r="K102">
-        <v>0.230598</v>
+        <v>0.186342</v>
       </c>
     </row>
     <row r="103">
@@ -3983,7 +3983,7 @@
         </is>
       </c>
       <c r="K103">
-        <v>0.177049</v>
+        <v>0.147602</v>
       </c>
     </row>
     <row r="104">
@@ -4018,7 +4018,7 @@
         </is>
       </c>
       <c r="K104">
-        <v>0.264559</v>
+        <v>0.230802</v>
       </c>
     </row>
     <row r="105">
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="K105">
-        <v>0.153855</v>
+        <v>0.126045</v>
       </c>
     </row>
     <row r="106">
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="K106">
-        <v>0.130143</v>
+        <v>0.113278</v>
       </c>
     </row>
     <row r="107">
@@ -4123,7 +4123,7 @@
         </is>
       </c>
       <c r="K107">
-        <v>0.201009</v>
+        <v>0.195747</v>
       </c>
     </row>
     <row r="108">
@@ -4158,7 +4158,7 @@
         </is>
       </c>
       <c r="K108">
-        <v>0.174714</v>
+        <v>0.1613</v>
       </c>
     </row>
     <row r="109">
@@ -4193,7 +4193,7 @@
         </is>
       </c>
       <c r="K109">
-        <v>0.194542</v>
+        <v>0.207734</v>
       </c>
     </row>
     <row r="110">
@@ -4228,7 +4228,7 @@
         </is>
       </c>
       <c r="K110">
-        <v>0.305985</v>
+        <v>0.340321</v>
       </c>
     </row>
     <row r="111">
@@ -4263,7 +4263,7 @@
         </is>
       </c>
       <c r="K111">
-        <v>0.264265</v>
+        <v>0.44375</v>
       </c>
     </row>
     <row r="112">
@@ -4298,7 +4298,7 @@
         </is>
       </c>
       <c r="K112">
-        <v>0.248669</v>
+        <v>0.257492</v>
       </c>
     </row>
     <row r="113">
@@ -4333,7 +4333,7 @@
         </is>
       </c>
       <c r="K113">
-        <v>0.224242</v>
+        <v>0.196452</v>
       </c>
     </row>
     <row r="114">
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="K114">
-        <v>0.178946</v>
+        <v>0.146301</v>
       </c>
     </row>
     <row r="115">
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="K115">
-        <v>0.197312</v>
+        <v>0.153358</v>
       </c>
     </row>
     <row r="116">
@@ -4438,7 +4438,7 @@
         </is>
       </c>
       <c r="K116">
-        <v>0.161019</v>
+        <v>0.14583</v>
       </c>
     </row>
     <row r="117">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="K117">
-        <v>0.217845</v>
+        <v>0.240251</v>
       </c>
     </row>
     <row r="118">
@@ -4508,7 +4508,7 @@
         </is>
       </c>
       <c r="K118">
-        <v>0.163229</v>
+        <v>0.128368</v>
       </c>
     </row>
     <row r="119">
@@ -4543,7 +4543,7 @@
         </is>
       </c>
       <c r="K119">
-        <v>0.160552</v>
+        <v>0.126766</v>
       </c>
     </row>
     <row r="120">
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="K120">
-        <v>0.156312</v>
+        <v>0.128016</v>
       </c>
     </row>
     <row r="121">
@@ -4613,7 +4613,7 @@
         </is>
       </c>
       <c r="K121">
-        <v>0.256777</v>
+        <v>0.152572</v>
       </c>
     </row>
     <row r="122">
@@ -4648,7 +4648,7 @@
         </is>
       </c>
       <c r="K122">
-        <v>0.202985</v>
+        <v>0.159845</v>
       </c>
     </row>
     <row r="123">
@@ -4683,7 +4683,7 @@
         </is>
       </c>
       <c r="K123">
-        <v>0.151373</v>
+        <v>0.120148</v>
       </c>
     </row>
     <row r="124">
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="K124">
-        <v>0.16608</v>
+        <v>0.128227</v>
       </c>
     </row>
     <row r="125">
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="K125">
-        <v>0.153085</v>
+        <v>0.120868</v>
       </c>
     </row>
     <row r="126">
@@ -4788,7 +4788,7 @@
         </is>
       </c>
       <c r="K126">
-        <v>0.176027</v>
+        <v>0.129945</v>
       </c>
     </row>
     <row r="127">
@@ -4823,7 +4823,7 @@
         </is>
       </c>
       <c r="K127">
-        <v>0.174321</v>
+        <v>0.157975</v>
       </c>
     </row>
     <row r="128">
@@ -4858,7 +4858,7 @@
         </is>
       </c>
       <c r="K128">
-        <v>0.158749</v>
+        <v>0.11947</v>
       </c>
     </row>
     <row r="129">
@@ -4893,7 +4893,7 @@
         </is>
       </c>
       <c r="K129">
-        <v>0.20501</v>
+        <v>0.157084</v>
       </c>
     </row>
     <row r="130">
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="K130">
-        <v>0.251039</v>
+        <v>0.241438</v>
       </c>
     </row>
     <row r="131">
@@ -4963,7 +4963,7 @@
         </is>
       </c>
       <c r="K131">
-        <v>0.178301</v>
+        <v>0.144748</v>
       </c>
     </row>
     <row r="132">
@@ -4998,7 +4998,7 @@
         </is>
       </c>
       <c r="K132">
-        <v>0.15348</v>
+        <v>0.129727</v>
       </c>
     </row>
     <row r="133">
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="K133">
-        <v>0.17228</v>
+        <v>0.134037</v>
       </c>
     </row>
     <row r="134">
@@ -5068,7 +5068,7 @@
         </is>
       </c>
       <c r="K134">
-        <v>0.174292</v>
+        <v>0.1717</v>
       </c>
     </row>
     <row r="135">
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="K135">
-        <v>0.236574</v>
+        <v>0.159084</v>
       </c>
     </row>
     <row r="136">
@@ -5138,7 +5138,7 @@
         </is>
       </c>
       <c r="K136">
-        <v>0.153066</v>
+        <v>0.141649</v>
       </c>
     </row>
     <row r="137">
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="K137">
-        <v>0.155453</v>
+        <v>0.129424</v>
       </c>
     </row>
     <row r="138">
@@ -5208,7 +5208,7 @@
         </is>
       </c>
       <c r="K138">
-        <v>0.156347</v>
+        <v>0.13594</v>
       </c>
     </row>
     <row r="139">
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="K139">
-        <v>0.315054</v>
+        <v>0.27497</v>
       </c>
     </row>
     <row r="140">
@@ -5278,7 +5278,7 @@
         </is>
       </c>
       <c r="K140">
-        <v>0.153651</v>
+        <v>0.144381</v>
       </c>
     </row>
     <row r="141">
@@ -5313,7 +5313,7 @@
         </is>
       </c>
       <c r="K141">
-        <v>0.162925</v>
+        <v>0.139575</v>
       </c>
     </row>
     <row r="142">
@@ -5348,7 +5348,7 @@
         </is>
       </c>
       <c r="K142">
-        <v>0.146617</v>
+        <v>0.139811</v>
       </c>
     </row>
     <row r="143">
@@ -5383,7 +5383,7 @@
         </is>
       </c>
       <c r="K143">
-        <v>0.149755</v>
+        <v>0.141318</v>
       </c>
     </row>
     <row r="144">
@@ -5418,7 +5418,7 @@
         </is>
       </c>
       <c r="K144">
-        <v>0.118771</v>
+        <v>0.117312</v>
       </c>
     </row>
     <row r="145">
@@ -5453,7 +5453,7 @@
         </is>
       </c>
       <c r="K145">
-        <v>0.15973</v>
+        <v>0.12239</v>
       </c>
     </row>
     <row r="146">
@@ -5488,7 +5488,7 @@
         </is>
       </c>
       <c r="K146">
-        <v>0.200467</v>
+        <v>0.130823</v>
       </c>
     </row>
     <row r="147">
@@ -5523,7 +5523,7 @@
         </is>
       </c>
       <c r="K147">
-        <v>0.253747</v>
+        <v>0.15653</v>
       </c>
     </row>
     <row r="148">
@@ -5558,7 +5558,7 @@
         </is>
       </c>
       <c r="K148">
-        <v>0.171815</v>
+        <v>0.148011</v>
       </c>
     </row>
     <row r="149">
@@ -5593,7 +5593,7 @@
         </is>
       </c>
       <c r="K149">
-        <v>0.206441</v>
+        <v>0.141942</v>
       </c>
     </row>
     <row r="150">
@@ -5628,7 +5628,7 @@
         </is>
       </c>
       <c r="K150">
-        <v>0.155007</v>
+        <v>0.127132</v>
       </c>
     </row>
     <row r="151">
@@ -5663,7 +5663,7 @@
         </is>
       </c>
       <c r="K151">
-        <v>0.192004</v>
+        <v>0.145321</v>
       </c>
     </row>
     <row r="152">
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="K152">
-        <v>0.196443</v>
+        <v>0.193429</v>
       </c>
     </row>
     <row r="153">
@@ -5733,7 +5733,7 @@
         </is>
       </c>
       <c r="K153">
-        <v>0.152101</v>
+        <v>0.145712</v>
       </c>
     </row>
     <row r="154">
@@ -5768,7 +5768,7 @@
         </is>
       </c>
       <c r="K154">
-        <v>0.157079</v>
+        <v>0.154259</v>
       </c>
     </row>
     <row r="155">
@@ -5803,7 +5803,7 @@
         </is>
       </c>
       <c r="K155">
-        <v>0.266187</v>
+        <v>0.163436</v>
       </c>
     </row>
     <row r="156">
@@ -5838,7 +5838,7 @@
         </is>
       </c>
       <c r="K156">
-        <v>0.187442</v>
+        <v>0.218792</v>
       </c>
     </row>
     <row r="157">
@@ -5873,7 +5873,7 @@
         </is>
       </c>
       <c r="K157">
-        <v>0.215615</v>
+        <v>0.138534</v>
       </c>
     </row>
     <row r="158">
@@ -5908,7 +5908,7 @@
         </is>
       </c>
       <c r="K158">
-        <v>0.192139</v>
+        <v>0.16376</v>
       </c>
     </row>
     <row r="159">
@@ -5943,7 +5943,7 @@
         </is>
       </c>
       <c r="K159">
-        <v>0.184702</v>
+        <v>0.125365</v>
       </c>
     </row>
     <row r="160">
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="K160">
-        <v>0.223354</v>
+        <v>0.15346</v>
       </c>
     </row>
     <row r="161">
@@ -6013,7 +6013,7 @@
         </is>
       </c>
       <c r="K161">
-        <v>0.17897</v>
+        <v>0.136245</v>
       </c>
     </row>
     <row r="162">
@@ -6048,7 +6048,7 @@
         </is>
       </c>
       <c r="K162">
-        <v>0.161617</v>
+        <v>0.132767</v>
       </c>
     </row>
     <row r="163">
@@ -6083,7 +6083,7 @@
         </is>
       </c>
       <c r="K163">
-        <v>0.289646</v>
+        <v>0.188291</v>
       </c>
     </row>
     <row r="164">
@@ -6118,7 +6118,7 @@
         </is>
       </c>
       <c r="K164">
-        <v>0.195091</v>
+        <v>0.188851</v>
       </c>
     </row>
     <row r="165">
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="K165">
-        <v>0.171823</v>
+        <v>0.159759</v>
       </c>
     </row>
     <row r="166">
@@ -6188,7 +6188,7 @@
         </is>
       </c>
       <c r="K166">
-        <v>0.187891</v>
+        <v>0.18243</v>
       </c>
     </row>
     <row r="167">
@@ -6223,7 +6223,7 @@
         </is>
       </c>
       <c r="K167">
-        <v>0.214073</v>
+        <v>0.158412</v>
       </c>
     </row>
     <row r="168">
@@ -6258,7 +6258,7 @@
         </is>
       </c>
       <c r="K168">
-        <v>0.171079</v>
+        <v>0.145601</v>
       </c>
     </row>
     <row r="169">
@@ -6293,7 +6293,7 @@
         </is>
       </c>
       <c r="K169">
-        <v>0.180902</v>
+        <v>0.16458</v>
       </c>
     </row>
     <row r="170">
@@ -6328,7 +6328,7 @@
         </is>
       </c>
       <c r="K170">
-        <v>0.233109</v>
+        <v>0.186198</v>
       </c>
     </row>
     <row r="171">
@@ -6363,7 +6363,7 @@
         </is>
       </c>
       <c r="K171">
-        <v>0.240769</v>
+        <v>0.200246</v>
       </c>
     </row>
     <row r="172">
@@ -6398,7 +6398,7 @@
         </is>
       </c>
       <c r="K172">
-        <v>0.200183</v>
+        <v>0.181764</v>
       </c>
     </row>
     <row r="173">
@@ -6433,7 +6433,7 @@
         </is>
       </c>
       <c r="K173">
-        <v>0.159333</v>
+        <v>0.140169</v>
       </c>
     </row>
     <row r="174">
@@ -6468,7 +6468,7 @@
         </is>
       </c>
       <c r="K174">
-        <v>0.167206</v>
+        <v>0.149561</v>
       </c>
     </row>
     <row r="175">
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="K175">
-        <v>0.155427</v>
+        <v>0.118485</v>
       </c>
     </row>
     <row r="176">
@@ -6538,7 +6538,7 @@
         </is>
       </c>
       <c r="K176">
-        <v>0.146627</v>
+        <v>0.14373</v>
       </c>
     </row>
     <row r="177">
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="K177">
-        <v>0.157436</v>
+        <v>0.147422</v>
       </c>
     </row>
     <row r="178">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="K178">
-        <v>0.148217</v>
+        <v>0.298596</v>
       </c>
     </row>
     <row r="179">
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="K179">
-        <v>0.156618</v>
+        <v>0.146895</v>
       </c>
     </row>
     <row r="180">
@@ -6678,7 +6678,7 @@
         </is>
       </c>
       <c r="K180">
-        <v>0.147961</v>
+        <v>0.139623</v>
       </c>
     </row>
     <row r="181">
@@ -6713,7 +6713,7 @@
         </is>
       </c>
       <c r="K181">
-        <v>0.143813</v>
+        <v>0.127505</v>
       </c>
     </row>
     <row r="182">
@@ -6748,7 +6748,7 @@
         </is>
       </c>
       <c r="K182">
-        <v>0.205653</v>
+        <v>0.150076</v>
       </c>
     </row>
     <row r="183">
@@ -6783,7 +6783,7 @@
         </is>
       </c>
       <c r="K183">
-        <v>0.154203</v>
+        <v>0.126842</v>
       </c>
     </row>
     <row r="184">
@@ -6818,7 +6818,7 @@
         </is>
       </c>
       <c r="K184">
-        <v>0.178784</v>
+        <v>0.146981</v>
       </c>
     </row>
     <row r="185">
@@ -6853,7 +6853,7 @@
         </is>
       </c>
       <c r="K185">
-        <v>0.1831</v>
+        <v>0.162436</v>
       </c>
     </row>
     <row r="186">
@@ -6888,7 +6888,7 @@
         </is>
       </c>
       <c r="K186">
-        <v>0.257753</v>
+        <v>0.207391</v>
       </c>
     </row>
     <row r="187">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>NL32</t>
+          <t>NL31</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -6923,7 +6923,7 @@
         </is>
       </c>
       <c r="K187">
-        <v>0.132646</v>
+        <v>0.161501</v>
       </c>
     </row>
     <row r="188">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>NL34</t>
+          <t>NL32</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -6958,7 +6958,7 @@
         </is>
       </c>
       <c r="K188">
-        <v>0.170863</v>
+        <v>0.151704</v>
       </c>
     </row>
     <row r="189">
@@ -6969,7 +6969,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>NL41</t>
+          <t>NL33</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -6993,7 +6993,7 @@
         </is>
       </c>
       <c r="K189">
-        <v>0.216237</v>
+        <v>0.149747</v>
       </c>
     </row>
     <row r="190">
@@ -7004,7 +7004,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>NL42</t>
+          <t>NL34</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -7028,18 +7028,18 @@
         </is>
       </c>
       <c r="K190">
-        <v>0.173215</v>
+        <v>0.137152</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>PL21</t>
+          <t>NL41</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -7063,18 +7063,18 @@
         </is>
       </c>
       <c r="K191">
-        <v>0.140062</v>
+        <v>0.177165</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>PL22</t>
+          <t>NL42</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -7098,7 +7098,7 @@
         </is>
       </c>
       <c r="K192">
-        <v>0.186416</v>
+        <v>0.132375</v>
       </c>
     </row>
     <row r="193">
@@ -7109,7 +7109,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>PL41</t>
+          <t>PL21</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -7133,7 +7133,7 @@
         </is>
       </c>
       <c r="K193">
-        <v>0.161383</v>
+        <v>0.116352</v>
       </c>
     </row>
     <row r="194">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>PL42</t>
+          <t>PL22</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -7168,7 +7168,7 @@
         </is>
       </c>
       <c r="K194">
-        <v>0.148376</v>
+        <v>0.117916</v>
       </c>
     </row>
     <row r="195">
@@ -7179,7 +7179,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>PL43</t>
+          <t>PL41</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -7203,7 +7203,7 @@
         </is>
       </c>
       <c r="K195">
-        <v>0.167092</v>
+        <v>0.133021</v>
       </c>
     </row>
     <row r="196">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>PL51</t>
+          <t>PL42</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -7238,7 +7238,7 @@
         </is>
       </c>
       <c r="K196">
-        <v>0.183988</v>
+        <v>0.122523</v>
       </c>
     </row>
     <row r="197">
@@ -7249,7 +7249,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>PL52</t>
+          <t>PL43</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -7273,7 +7273,7 @@
         </is>
       </c>
       <c r="K197">
-        <v>0.153383</v>
+        <v>0.121973</v>
       </c>
     </row>
     <row r="198">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>PL61</t>
+          <t>PL51</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -7308,7 +7308,7 @@
         </is>
       </c>
       <c r="K198">
-        <v>0.155707</v>
+        <v>0.121802</v>
       </c>
     </row>
     <row r="199">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>PL62</t>
+          <t>PL52</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -7343,7 +7343,7 @@
         </is>
       </c>
       <c r="K199">
-        <v>0.176669</v>
+        <v>0.113449</v>
       </c>
     </row>
     <row r="200">
@@ -7354,7 +7354,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>PL63</t>
+          <t>PL61</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -7378,7 +7378,7 @@
         </is>
       </c>
       <c r="K200">
-        <v>0.15872</v>
+        <v>0.133537</v>
       </c>
     </row>
     <row r="201">
@@ -7389,7 +7389,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>PL71</t>
+          <t>PL62</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -7413,7 +7413,7 @@
         </is>
       </c>
       <c r="K201">
-        <v>0.123905</v>
+        <v>0.156179</v>
       </c>
     </row>
     <row r="202">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>PL72</t>
+          <t>PL63</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -7448,7 +7448,7 @@
         </is>
       </c>
       <c r="K202">
-        <v>0.200415</v>
+        <v>0.13628</v>
       </c>
     </row>
     <row r="203">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>PL81</t>
+          <t>PL71</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -7483,7 +7483,7 @@
         </is>
       </c>
       <c r="K203">
-        <v>0.16253</v>
+        <v>0.119696</v>
       </c>
     </row>
     <row r="204">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>PL82</t>
+          <t>PL72</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -7518,7 +7518,7 @@
         </is>
       </c>
       <c r="K204">
-        <v>0.179287</v>
+        <v>0.140064</v>
       </c>
     </row>
     <row r="205">
@@ -7529,7 +7529,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>PL84</t>
+          <t>PL81</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -7553,7 +7553,7 @@
         </is>
       </c>
       <c r="K205">
-        <v>0.158488</v>
+        <v>0.149336</v>
       </c>
     </row>
     <row r="206">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>PL91</t>
+          <t>PL82</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="K206">
-        <v>0.138762</v>
+        <v>0.123083</v>
       </c>
     </row>
     <row r="207">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>PL92</t>
+          <t>PL84</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -7623,18 +7623,18 @@
         </is>
       </c>
       <c r="K207">
-        <v>0.176526</v>
+        <v>0.138084</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>PT11</t>
+          <t>PL91</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -7658,18 +7658,18 @@
         </is>
       </c>
       <c r="K208">
-        <v>0.225222</v>
+        <v>0.129674</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>PT15</t>
+          <t>PL92</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -7693,7 +7693,7 @@
         </is>
       </c>
       <c r="K209">
-        <v>0.212816</v>
+        <v>0.186237</v>
       </c>
     </row>
     <row r="210">
@@ -7704,7 +7704,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>PT20</t>
+          <t>PT11</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -7728,7 +7728,7 @@
         </is>
       </c>
       <c r="K210">
-        <v>0.465082</v>
+        <v>0.222583</v>
       </c>
     </row>
     <row r="211">
@@ -7739,7 +7739,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>PT30</t>
+          <t>PT15</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -7763,18 +7763,18 @@
         </is>
       </c>
       <c r="K211">
-        <v>0.354319</v>
+        <v>0.253121</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>RO11</t>
+          <t>PT16</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -7798,18 +7798,18 @@
         </is>
       </c>
       <c r="K212">
-        <v>0.137577</v>
+        <v>0.140525</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>RO12</t>
+          <t>PT17</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -7833,18 +7833,18 @@
         </is>
       </c>
       <c r="K213">
-        <v>0.193637</v>
+        <v>0.13514</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>RO21</t>
+          <t>PT18</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -7868,18 +7868,18 @@
         </is>
       </c>
       <c r="K214">
-        <v>0.163114</v>
+        <v>0.212273</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>RO22</t>
+          <t>PT20</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -7903,18 +7903,18 @@
         </is>
       </c>
       <c r="K215">
-        <v>0.168466</v>
+        <v>0.182323</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>RO31</t>
+          <t>PT30</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -7938,7 +7938,7 @@
         </is>
       </c>
       <c r="K216">
-        <v>0.190943</v>
+        <v>0.20076</v>
       </c>
     </row>
     <row r="217">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>RO32</t>
+          <t>RO11</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="K217">
-        <v>0.15464</v>
+        <v>0.113467</v>
       </c>
     </row>
     <row r="218">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>RO41</t>
+          <t>RO12</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -8008,7 +8008,7 @@
         </is>
       </c>
       <c r="K218">
-        <v>0.173705</v>
+        <v>0.129595</v>
       </c>
     </row>
     <row r="219">
@@ -8019,7 +8019,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>RO42</t>
+          <t>RO21</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -8043,18 +8043,18 @@
         </is>
       </c>
       <c r="K219">
-        <v>0.228555</v>
+        <v>0.151243</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>SE11</t>
+          <t>RO22</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -8078,18 +8078,18 @@
         </is>
       </c>
       <c r="K220">
-        <v>0.226079</v>
+        <v>0.132537</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>SE12</t>
+          <t>RO31</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -8113,18 +8113,18 @@
         </is>
       </c>
       <c r="K221">
-        <v>0.262648</v>
+        <v>0.130364</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>SE21</t>
+          <t>RO32</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -8148,18 +8148,18 @@
         </is>
       </c>
       <c r="K222">
-        <v>0.267779</v>
+        <v>0.133996</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>SE22</t>
+          <t>RO41</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -8183,18 +8183,18 @@
         </is>
       </c>
       <c r="K223">
-        <v>0.186725</v>
+        <v>0.132627</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>SE23</t>
+          <t>RO42</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -8218,7 +8218,7 @@
         </is>
       </c>
       <c r="K224">
-        <v>0.307863</v>
+        <v>0.170174</v>
       </c>
     </row>
     <row r="225">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>SE31</t>
+          <t>SE11</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="K225">
-        <v>0.209993</v>
+        <v>0.143379</v>
       </c>
     </row>
     <row r="226">
@@ -8264,7 +8264,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>SE32</t>
+          <t>SE12</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
@@ -8288,7 +8288,7 @@
         </is>
       </c>
       <c r="K226">
-        <v>0.215462</v>
+        <v>0.170123</v>
       </c>
     </row>
     <row r="227">
@@ -8299,7 +8299,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>SE33</t>
+          <t>SE21</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -8323,18 +8323,18 @@
         </is>
       </c>
       <c r="K227">
-        <v>0.200683</v>
+        <v>0.194633</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>SI03</t>
+          <t>SE22</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
@@ -8358,18 +8358,18 @@
         </is>
       </c>
       <c r="K228">
-        <v>0.200494</v>
+        <v>0.135315</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>SI04</t>
+          <t>SE23</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
@@ -8393,18 +8393,18 @@
         </is>
       </c>
       <c r="K229">
-        <v>0.134848</v>
+        <v>0.17633</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>SK01</t>
+          <t>SE31</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
@@ -8428,18 +8428,18 @@
         </is>
       </c>
       <c r="K230">
-        <v>0.249301</v>
+        <v>0.191803</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>SK02</t>
+          <t>SE32</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -8463,18 +8463,18 @@
         </is>
       </c>
       <c r="K231">
-        <v>0.222</v>
+        <v>0.174078</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>SK03</t>
+          <t>SE33</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -8498,42 +8498,217 @@
         </is>
       </c>
       <c r="K232">
-        <v>0.241484</v>
+        <v>0.149931</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>SI03</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Diversification</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>HHI_Employment</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>Index (0-1)</t>
+        </is>
+      </c>
+      <c r="K233">
+        <v>0.153569</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>SI04</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Diversification</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>HHI_Employment</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>Index (0-1)</t>
+        </is>
+      </c>
+      <c r="K234">
+        <v>0.121588</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
           <t>SK</t>
         </is>
       </c>
-      <c r="C233" t="inlineStr">
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>SK01</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Diversification</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>HHI_Employment</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>Index (0-1)</t>
+        </is>
+      </c>
+      <c r="K235">
+        <v>0.179585</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>SK02</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Diversification</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>HHI_Employment</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>Index (0-1)</t>
+        </is>
+      </c>
+      <c r="K236">
+        <v>0.14437</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>SK03</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Diversification</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>HHI_Employment</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>Index (0-1)</t>
+        </is>
+      </c>
+      <c r="K237">
+        <v>0.148639</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
         <is>
           <t>SK04</t>
         </is>
       </c>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>Vulnerability</t>
-        </is>
-      </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>Diversification</t>
-        </is>
-      </c>
-      <c r="I233" t="inlineStr">
-        <is>
-          <t>HHI_Employment</t>
-        </is>
-      </c>
-      <c r="J233" t="inlineStr">
-        <is>
-          <t>Index (0-1)</t>
-        </is>
-      </c>
-      <c r="K233">
-        <v>0.19498</v>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Diversification</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>HHI_Employment</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>Index (0-1)</t>
+        </is>
+      </c>
+      <c r="K238">
+        <v>0.136538</v>
       </c>
     </row>
   </sheetData>

--- a/Code and data/Initial data/Non sector data/DIVERS-HHI.xlsx
+++ b/Code and data/Initial data/Non sector data/DIVERS-HHI.xlsx
@@ -448,7 +448,7 @@
         </is>
       </c>
       <c r="K2">
-        <v>0.121529</v>
+        <v>0.132278</v>
       </c>
     </row>
     <row r="3">
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="K3">
-        <v>0.137468</v>
+        <v>0.131858</v>
       </c>
     </row>
     <row r="4">
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="K4">
-        <v>0.122471</v>
+        <v>0.135368</v>
       </c>
     </row>
     <row r="5">
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="K5">
-        <v>0.155148</v>
+        <v>0.174665</v>
       </c>
     </row>
     <row r="6">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="K6">
-        <v>0.138486</v>
+        <v>0.133742</v>
       </c>
     </row>
     <row r="7">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="K7">
-        <v>0.14705</v>
+        <v>0.14231</v>
       </c>
     </row>
     <row r="8">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="K8">
-        <v>0.134785</v>
+        <v>0.15551</v>
       </c>
     </row>
     <row r="9">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="K9">
-        <v>0.138331</v>
+        <v>0.134223</v>
       </c>
     </row>
     <row r="10">
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="K10">
-        <v>0.191838</v>
+        <v>0.225745</v>
       </c>
     </row>
     <row r="11">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="K11">
-        <v>0.140125</v>
+        <v>0.157432</v>
       </c>
     </row>
     <row r="12">
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="K12">
-        <v>0.133513</v>
+        <v>0.131905</v>
       </c>
     </row>
     <row r="13">
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="K13">
-        <v>0.139067</v>
+        <v>0.135972</v>
       </c>
     </row>
     <row r="14">
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="K14">
-        <v>0.121817</v>
+        <v>0.119028</v>
       </c>
     </row>
     <row r="15">
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="K15">
-        <v>0.167608</v>
+        <v>0.183541</v>
       </c>
     </row>
     <row r="16">
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="K16">
-        <v>0.144017</v>
+        <v>0.152252</v>
       </c>
     </row>
     <row r="17">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="K17">
-        <v>0.42393</v>
+        <v>0.362997</v>
       </c>
     </row>
     <row r="18">
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="K18">
-        <v>0.131302</v>
+        <v>0.126658</v>
       </c>
     </row>
     <row r="19">
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="K19">
-        <v>0.149566</v>
+        <v>0.140171</v>
       </c>
     </row>
     <row r="20">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="K20">
-        <v>0.165223</v>
+        <v>0.209224</v>
       </c>
     </row>
     <row r="21">
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="K21">
-        <v>0.152519</v>
+        <v>0.206353</v>
       </c>
     </row>
     <row r="22">
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="K22">
-        <v>0.13576</v>
+        <v>0.125744</v>
       </c>
     </row>
     <row r="23">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="K23">
-        <v>0.138531</v>
+        <v>0.139243</v>
       </c>
     </row>
     <row r="24">
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="K24">
-        <v>0.118754</v>
+        <v>0.118895</v>
       </c>
     </row>
     <row r="25">
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="K25">
-        <v>0.164345</v>
+        <v>0.177649</v>
       </c>
     </row>
     <row r="26">
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="K26">
-        <v>0.12117</v>
+        <v>0.121501</v>
       </c>
     </row>
     <row r="27">
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="K27">
-        <v>0.123494</v>
+        <v>0.123718</v>
       </c>
     </row>
     <row r="28">
@@ -1358,7 +1358,7 @@
         </is>
       </c>
       <c r="K28">
-        <v>0.227329</v>
+        <v>0.230423</v>
       </c>
     </row>
     <row r="29">
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="K29">
-        <v>0.126587</v>
+        <v>0.127091</v>
       </c>
     </row>
     <row r="30">
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="K30">
-        <v>0.167656</v>
+        <v>0.17169</v>
       </c>
     </row>
     <row r="31">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="K31">
-        <v>0.150895</v>
+        <v>0.152301</v>
       </c>
     </row>
     <row r="32">
@@ -1498,7 +1498,7 @@
         </is>
       </c>
       <c r="K32">
-        <v>0.124235</v>
+        <v>0.123154</v>
       </c>
     </row>
     <row r="33">
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="K33">
-        <v>0.143447</v>
+        <v>0.141666</v>
       </c>
     </row>
     <row r="34">
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="K34">
-        <v>0.15095</v>
+        <v>0.150377</v>
       </c>
     </row>
     <row r="35">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="K35">
-        <v>0.152971</v>
+        <v>0.155549</v>
       </c>
     </row>
     <row r="36">
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="K36">
-        <v>0.139886</v>
+        <v>0.138429</v>
       </c>
     </row>
     <row r="37">
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="K37">
-        <v>0.227259</v>
+        <v>0.22813</v>
       </c>
     </row>
     <row r="38">
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="K38">
-        <v>0.159238</v>
+        <v>0.159519</v>
       </c>
     </row>
     <row r="39">
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="K39">
-        <v>0.205857</v>
+        <v>0.205091</v>
       </c>
     </row>
     <row r="40">
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="K40">
-        <v>0.197076</v>
+        <v>0.189079</v>
       </c>
     </row>
     <row r="41">
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="K41">
-        <v>0.160635</v>
+        <v>0.163098</v>
       </c>
     </row>
     <row r="42">
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="K42">
-        <v>0.172019</v>
+        <v>0.177472</v>
       </c>
     </row>
     <row r="43">
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="K43">
-        <v>0.163687</v>
+        <v>0.166347</v>
       </c>
     </row>
     <row r="44">
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c r="K44">
-        <v>0.143652</v>
+        <v>0.146964</v>
       </c>
     </row>
     <row r="45">
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="K45">
-        <v>0.161712</v>
+        <v>0.163321</v>
       </c>
     </row>
     <row r="46">
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="K46">
-        <v>0.167538</v>
+        <v>0.162811</v>
       </c>
     </row>
     <row r="47">
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="K47">
-        <v>0.181217</v>
+        <v>0.18251</v>
       </c>
     </row>
     <row r="48">
@@ -2058,7 +2058,7 @@
         </is>
       </c>
       <c r="K48">
-        <v>0.147</v>
+        <v>0.145838</v>
       </c>
     </row>
     <row r="49">
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="K49">
-        <v>0.120819</v>
+        <v>0.123379</v>
       </c>
     </row>
     <row r="50">
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="K50">
-        <v>0.218469</v>
+        <v>0.220392</v>
       </c>
     </row>
     <row r="51">
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="K51">
-        <v>0.177181</v>
+        <v>0.159472</v>
       </c>
     </row>
     <row r="52">
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="K52">
-        <v>0.123155</v>
+        <v>0.12441</v>
       </c>
     </row>
     <row r="53">
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="K53">
-        <v>0.181638</v>
+        <v>0.187134</v>
       </c>
     </row>
     <row r="54">
@@ -2268,7 +2268,7 @@
         </is>
       </c>
       <c r="K54">
-        <v>0.139977</v>
+        <v>0.143162</v>
       </c>
     </row>
     <row r="55">
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="K55">
-        <v>0.162695</v>
+        <v>0.162584</v>
       </c>
     </row>
     <row r="56">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="K56">
-        <v>0.250938</v>
+        <v>0.257965</v>
       </c>
     </row>
     <row r="57">
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="K57">
-        <v>0.125818</v>
+        <v>0.125859</v>
       </c>
     </row>
     <row r="58">
@@ -2408,7 +2408,7 @@
         </is>
       </c>
       <c r="K58">
-        <v>0.163333</v>
+        <v>0.167059</v>
       </c>
     </row>
     <row r="59">
@@ -2443,7 +2443,7 @@
         </is>
       </c>
       <c r="K59">
-        <v>0.159676</v>
+        <v>0.161559</v>
       </c>
     </row>
     <row r="60">
@@ -2478,7 +2478,7 @@
         </is>
       </c>
       <c r="K60">
-        <v>0.151576</v>
+        <v>0.152571</v>
       </c>
     </row>
     <row r="61">
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="K61">
-        <v>0.124953</v>
+        <v>0.126323</v>
       </c>
     </row>
     <row r="62">
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="K62">
-        <v>0.150556</v>
+        <v>0.152712</v>
       </c>
     </row>
     <row r="63">
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="K63">
-        <v>0.153534</v>
+        <v>0.153126</v>
       </c>
     </row>
     <row r="64">
@@ -2618,7 +2618,7 @@
         </is>
       </c>
       <c r="K64">
-        <v>0.210853</v>
+        <v>0.211568</v>
       </c>
     </row>
     <row r="65">
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="K65">
-        <v>0.163591</v>
+        <v>0.165087</v>
       </c>
     </row>
     <row r="66">
@@ -2688,7 +2688,7 @@
         </is>
       </c>
       <c r="K66">
-        <v>0.176851</v>
+        <v>0.18165</v>
       </c>
     </row>
     <row r="67">
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="K67">
-        <v>0.144857</v>
+        <v>0.144596</v>
       </c>
     </row>
     <row r="68">
@@ -2758,7 +2758,7 @@
         </is>
       </c>
       <c r="K68">
-        <v>0.169338</v>
+        <v>0.171753</v>
       </c>
     </row>
     <row r="69">
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="K69">
-        <v>0.138103</v>
+        <v>0.140968</v>
       </c>
     </row>
     <row r="70">
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="K70">
-        <v>0.16958</v>
+        <v>0.169623</v>
       </c>
     </row>
     <row r="71">
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="K71">
-        <v>0.134341</v>
+        <v>0.137912</v>
       </c>
     </row>
     <row r="72">
@@ -2898,7 +2898,7 @@
         </is>
       </c>
       <c r="K72">
-        <v>0.132073</v>
+        <v>0.129865</v>
       </c>
     </row>
     <row r="73">
@@ -2933,7 +2933,7 @@
         </is>
       </c>
       <c r="K73">
-        <v>0.13725</v>
+        <v>0.144296</v>
       </c>
     </row>
     <row r="74">
@@ -2968,7 +2968,7 @@
         </is>
       </c>
       <c r="K74">
-        <v>0.14312</v>
+        <v>0.143093</v>
       </c>
     </row>
     <row r="75">
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="K75">
-        <v>0.200622</v>
+        <v>0.217892</v>
       </c>
     </row>
     <row r="76">
@@ -3038,7 +3038,7 @@
         </is>
       </c>
       <c r="K76">
-        <v>0.162131</v>
+        <v>0.167811</v>
       </c>
     </row>
     <row r="77">
@@ -3073,7 +3073,7 @@
         </is>
       </c>
       <c r="K77">
-        <v>0.191187</v>
+        <v>0.202632</v>
       </c>
     </row>
     <row r="78">
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="K78">
-        <v>0.215689</v>
+        <v>0.22385</v>
       </c>
     </row>
     <row r="79">
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="K79">
-        <v>0.188896</v>
+        <v>0.194624</v>
       </c>
     </row>
     <row r="80">
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="K80">
-        <v>0.130707</v>
+        <v>0.129598</v>
       </c>
     </row>
     <row r="81">
@@ -3213,7 +3213,7 @@
         </is>
       </c>
       <c r="K81">
-        <v>0.141031</v>
+        <v>0.139204</v>
       </c>
     </row>
     <row r="82">
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="K82">
-        <v>0.387697</v>
+        <v>0.424324</v>
       </c>
     </row>
     <row r="83">
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="K83">
-        <v>0.506915</v>
+        <v>0.165765</v>
       </c>
     </row>
     <row r="84">
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="K84">
-        <v>0.253826</v>
+        <v>0.267078</v>
       </c>
     </row>
     <row r="85">
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="K85">
-        <v>0.242592</v>
+        <v>0.254888</v>
       </c>
     </row>
     <row r="86">
@@ -3388,7 +3388,7 @@
         </is>
       </c>
       <c r="K86">
-        <v>0.230201</v>
+        <v>0.238127</v>
       </c>
     </row>
     <row r="87">
@@ -3423,7 +3423,7 @@
         </is>
       </c>
       <c r="K87">
-        <v>0.234657</v>
+        <v>0.249656</v>
       </c>
     </row>
     <row r="88">
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="K88">
-        <v>0.493784</v>
+        <v>0.531413</v>
       </c>
     </row>
     <row r="89">
@@ -3493,7 +3493,7 @@
         </is>
       </c>
       <c r="K89">
-        <v>0.297859</v>
+        <v>0.320031</v>
       </c>
     </row>
     <row r="90">
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="K90">
-        <v>0.241358</v>
+        <v>0.27067</v>
       </c>
     </row>
     <row r="91">
@@ -3563,7 +3563,7 @@
         </is>
       </c>
       <c r="K91">
-        <v>0.320083</v>
+        <v>0.331149</v>
       </c>
     </row>
     <row r="92">
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="K92">
-        <v>0.183064</v>
+        <v>0.190125</v>
       </c>
     </row>
     <row r="93">
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="K93">
-        <v>0.338042</v>
+        <v>0.337766</v>
       </c>
     </row>
     <row r="94">
@@ -3668,7 +3668,7 @@
         </is>
       </c>
       <c r="K94">
-        <v>0.152454</v>
+        <v>0.153438</v>
       </c>
     </row>
     <row r="95">
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="K95">
-        <v>0.156479</v>
+        <v>0.163681</v>
       </c>
     </row>
     <row r="96">
@@ -3738,7 +3738,7 @@
         </is>
       </c>
       <c r="K96">
-        <v>0.133851</v>
+        <v>0.138599</v>
       </c>
     </row>
     <row r="97">
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="K97">
-        <v>0.172947</v>
+        <v>0.174606</v>
       </c>
     </row>
     <row r="98">
@@ -3808,7 +3808,7 @@
         </is>
       </c>
       <c r="K98">
-        <v>0.15642</v>
+        <v>0.165542</v>
       </c>
     </row>
     <row r="99">
@@ -3843,7 +3843,7 @@
         </is>
       </c>
       <c r="K99">
-        <v>0.163787</v>
+        <v>0.181374</v>
       </c>
     </row>
     <row r="100">
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="K100">
-        <v>0.131812</v>
+        <v>0.129862</v>
       </c>
     </row>
     <row r="101">
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="K101">
-        <v>0.120485</v>
+        <v>0.11818</v>
       </c>
     </row>
     <row r="102">
@@ -3948,7 +3948,7 @@
         </is>
       </c>
       <c r="K102">
-        <v>0.186342</v>
+        <v>0.183675</v>
       </c>
     </row>
     <row r="103">
@@ -3983,7 +3983,7 @@
         </is>
       </c>
       <c r="K103">
-        <v>0.147602</v>
+        <v>0.146172</v>
       </c>
     </row>
     <row r="104">
@@ -4018,7 +4018,7 @@
         </is>
       </c>
       <c r="K104">
-        <v>0.230802</v>
+        <v>0.255825</v>
       </c>
     </row>
     <row r="105">
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="K105">
-        <v>0.126045</v>
+        <v>0.125843</v>
       </c>
     </row>
     <row r="106">
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="K106">
-        <v>0.113278</v>
+        <v>0.11416</v>
       </c>
     </row>
     <row r="107">
@@ -4123,7 +4123,7 @@
         </is>
       </c>
       <c r="K107">
-        <v>0.195747</v>
+        <v>0.193448</v>
       </c>
     </row>
     <row r="108">
@@ -4158,7 +4158,7 @@
         </is>
       </c>
       <c r="K108">
-        <v>0.1613</v>
+        <v>0.156843</v>
       </c>
     </row>
     <row r="109">
@@ -4193,7 +4193,7 @@
         </is>
       </c>
       <c r="K109">
-        <v>0.207734</v>
+        <v>0.217964</v>
       </c>
     </row>
     <row r="110">
@@ -4228,7 +4228,7 @@
         </is>
       </c>
       <c r="K110">
-        <v>0.340321</v>
+        <v>0.320154</v>
       </c>
     </row>
     <row r="111">
@@ -4263,7 +4263,7 @@
         </is>
       </c>
       <c r="K111">
-        <v>0.44375</v>
+        <v>0.233843</v>
       </c>
     </row>
     <row r="112">
@@ -4298,7 +4298,7 @@
         </is>
       </c>
       <c r="K112">
-        <v>0.257492</v>
+        <v>0.252684</v>
       </c>
     </row>
     <row r="113">
@@ -4333,7 +4333,7 @@
         </is>
       </c>
       <c r="K113">
-        <v>0.196452</v>
+        <v>0.184509</v>
       </c>
     </row>
     <row r="114">
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="K114">
-        <v>0.146301</v>
+        <v>0.154697</v>
       </c>
     </row>
     <row r="115">
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="K115">
-        <v>0.153358</v>
+        <v>0.146533</v>
       </c>
     </row>
     <row r="116">
@@ -4438,7 +4438,7 @@
         </is>
       </c>
       <c r="K116">
-        <v>0.14583</v>
+        <v>0.14328</v>
       </c>
     </row>
     <row r="117">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="K117">
-        <v>0.240251</v>
+        <v>0.21469</v>
       </c>
     </row>
     <row r="118">
@@ -4508,7 +4508,7 @@
         </is>
       </c>
       <c r="K118">
-        <v>0.128368</v>
+        <v>0.128037</v>
       </c>
     </row>
     <row r="119">
@@ -4543,7 +4543,7 @@
         </is>
       </c>
       <c r="K119">
-        <v>0.126766</v>
+        <v>0.129366</v>
       </c>
     </row>
     <row r="120">
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="K120">
-        <v>0.128016</v>
+        <v>0.129028</v>
       </c>
     </row>
     <row r="121">
@@ -4613,7 +4613,7 @@
         </is>
       </c>
       <c r="K121">
-        <v>0.152572</v>
+        <v>0.154844</v>
       </c>
     </row>
     <row r="122">
@@ -4648,7 +4648,7 @@
         </is>
       </c>
       <c r="K122">
-        <v>0.159845</v>
+        <v>0.154985</v>
       </c>
     </row>
     <row r="123">
@@ -4683,7 +4683,7 @@
         </is>
       </c>
       <c r="K123">
-        <v>0.120148</v>
+        <v>0.119935</v>
       </c>
     </row>
     <row r="124">
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="K124">
-        <v>0.128227</v>
+        <v>0.127373</v>
       </c>
     </row>
     <row r="125">
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="K125">
-        <v>0.120868</v>
+        <v>0.120366</v>
       </c>
     </row>
     <row r="126">
@@ -4788,7 +4788,7 @@
         </is>
       </c>
       <c r="K126">
-        <v>0.129945</v>
+        <v>0.130275</v>
       </c>
     </row>
     <row r="127">
@@ -4823,7 +4823,7 @@
         </is>
       </c>
       <c r="K127">
-        <v>0.157975</v>
+        <v>0.158251</v>
       </c>
     </row>
     <row r="128">
@@ -4858,7 +4858,7 @@
         </is>
       </c>
       <c r="K128">
-        <v>0.11947</v>
+        <v>0.11981</v>
       </c>
     </row>
     <row r="129">
@@ -4893,7 +4893,7 @@
         </is>
       </c>
       <c r="K129">
-        <v>0.157084</v>
+        <v>0.154638</v>
       </c>
     </row>
     <row r="130">
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="K130">
-        <v>0.241438</v>
+        <v>0.237638</v>
       </c>
     </row>
     <row r="131">
@@ -4963,7 +4963,7 @@
         </is>
       </c>
       <c r="K131">
-        <v>0.144748</v>
+        <v>0.144136</v>
       </c>
     </row>
     <row r="132">
@@ -4998,7 +4998,7 @@
         </is>
       </c>
       <c r="K132">
-        <v>0.129727</v>
+        <v>0.144978</v>
       </c>
     </row>
     <row r="133">
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="K133">
-        <v>0.134037</v>
+        <v>0.13857</v>
       </c>
     </row>
     <row r="134">
@@ -5068,7 +5068,7 @@
         </is>
       </c>
       <c r="K134">
-        <v>0.1717</v>
+        <v>0.169059</v>
       </c>
     </row>
     <row r="135">
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="K135">
-        <v>0.159084</v>
+        <v>0.163726</v>
       </c>
     </row>
     <row r="136">
@@ -5138,7 +5138,7 @@
         </is>
       </c>
       <c r="K136">
-        <v>0.141649</v>
+        <v>0.141728</v>
       </c>
     </row>
     <row r="137">
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="K137">
-        <v>0.129424</v>
+        <v>0.128309</v>
       </c>
     </row>
     <row r="138">
@@ -5208,7 +5208,7 @@
         </is>
       </c>
       <c r="K138">
-        <v>0.13594</v>
+        <v>0.135506</v>
       </c>
     </row>
     <row r="139">
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="K139">
-        <v>0.27497</v>
+        <v>0.317823</v>
       </c>
     </row>
     <row r="140">
@@ -5278,7 +5278,7 @@
         </is>
       </c>
       <c r="K140">
-        <v>0.144381</v>
+        <v>0.147568</v>
       </c>
     </row>
     <row r="141">
@@ -5313,7 +5313,7 @@
         </is>
       </c>
       <c r="K141">
-        <v>0.139575</v>
+        <v>0.141066</v>
       </c>
     </row>
     <row r="142">
@@ -5348,7 +5348,7 @@
         </is>
       </c>
       <c r="K142">
-        <v>0.139811</v>
+        <v>0.13807</v>
       </c>
     </row>
     <row r="143">
@@ -5383,7 +5383,7 @@
         </is>
       </c>
       <c r="K143">
-        <v>0.141318</v>
+        <v>0.141269</v>
       </c>
     </row>
     <row r="144">
@@ -5418,7 +5418,7 @@
         </is>
       </c>
       <c r="K144">
-        <v>0.117312</v>
+        <v>0.117785</v>
       </c>
     </row>
     <row r="145">
@@ -5453,7 +5453,7 @@
         </is>
       </c>
       <c r="K145">
-        <v>0.12239</v>
+        <v>0.133638</v>
       </c>
     </row>
     <row r="146">
@@ -5488,7 +5488,7 @@
         </is>
       </c>
       <c r="K146">
-        <v>0.130823</v>
+        <v>0.142748</v>
       </c>
     </row>
     <row r="147">
@@ -5523,7 +5523,7 @@
         </is>
       </c>
       <c r="K147">
-        <v>0.15653</v>
+        <v>0.161667</v>
       </c>
     </row>
     <row r="148">
@@ -5558,7 +5558,7 @@
         </is>
       </c>
       <c r="K148">
-        <v>0.148011</v>
+        <v>0.154678</v>
       </c>
     </row>
     <row r="149">
@@ -5593,7 +5593,7 @@
         </is>
       </c>
       <c r="K149">
-        <v>0.141942</v>
+        <v>0.140782</v>
       </c>
     </row>
     <row r="150">
@@ -5628,7 +5628,7 @@
         </is>
       </c>
       <c r="K150">
-        <v>0.127132</v>
+        <v>0.1286</v>
       </c>
     </row>
     <row r="151">
@@ -5663,7 +5663,7 @@
         </is>
       </c>
       <c r="K151">
-        <v>0.145321</v>
+        <v>0.150453</v>
       </c>
     </row>
     <row r="152">
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="K152">
-        <v>0.193429</v>
+        <v>0.180105</v>
       </c>
     </row>
     <row r="153">
@@ -5733,7 +5733,7 @@
         </is>
       </c>
       <c r="K153">
-        <v>0.145712</v>
+        <v>0.149412</v>
       </c>
     </row>
     <row r="154">
@@ -5768,7 +5768,7 @@
         </is>
       </c>
       <c r="K154">
-        <v>0.154259</v>
+        <v>0.158568</v>
       </c>
     </row>
     <row r="155">
@@ -5803,7 +5803,7 @@
         </is>
       </c>
       <c r="K155">
-        <v>0.163436</v>
+        <v>0.163316</v>
       </c>
     </row>
     <row r="156">
@@ -5838,7 +5838,7 @@
         </is>
       </c>
       <c r="K156">
-        <v>0.218792</v>
+        <v>0.160285</v>
       </c>
     </row>
     <row r="157">
@@ -5873,7 +5873,7 @@
         </is>
       </c>
       <c r="K157">
-        <v>0.138534</v>
+        <v>0.145702</v>
       </c>
     </row>
     <row r="158">
@@ -5908,7 +5908,7 @@
         </is>
       </c>
       <c r="K158">
-        <v>0.16376</v>
+        <v>0.164274</v>
       </c>
     </row>
     <row r="159">
@@ -5943,7 +5943,7 @@
         </is>
       </c>
       <c r="K159">
-        <v>0.125365</v>
+        <v>0.125463</v>
       </c>
     </row>
     <row r="160">
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="K160">
-        <v>0.15346</v>
+        <v>0.151638</v>
       </c>
     </row>
     <row r="161">
@@ -6013,7 +6013,7 @@
         </is>
       </c>
       <c r="K161">
-        <v>0.136245</v>
+        <v>0.138952</v>
       </c>
     </row>
     <row r="162">
@@ -6048,7 +6048,7 @@
         </is>
       </c>
       <c r="K162">
-        <v>0.132767</v>
+        <v>0.136272</v>
       </c>
     </row>
     <row r="163">
@@ -6083,7 +6083,7 @@
         </is>
       </c>
       <c r="K163">
-        <v>0.188291</v>
+        <v>0.179801</v>
       </c>
     </row>
     <row r="164">
@@ -6118,7 +6118,7 @@
         </is>
       </c>
       <c r="K164">
-        <v>0.188851</v>
+        <v>0.188655</v>
       </c>
     </row>
     <row r="165">
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="K165">
-        <v>0.159759</v>
+        <v>0.158041</v>
       </c>
     </row>
     <row r="166">
@@ -6188,7 +6188,7 @@
         </is>
       </c>
       <c r="K166">
-        <v>0.18243</v>
+        <v>0.174943</v>
       </c>
     </row>
     <row r="167">
@@ -6223,7 +6223,7 @@
         </is>
       </c>
       <c r="K167">
-        <v>0.158412</v>
+        <v>0.173496</v>
       </c>
     </row>
     <row r="168">
@@ -6258,7 +6258,7 @@
         </is>
       </c>
       <c r="K168">
-        <v>0.145601</v>
+        <v>0.149705</v>
       </c>
     </row>
     <row r="169">
@@ -6293,7 +6293,7 @@
         </is>
       </c>
       <c r="K169">
-        <v>0.16458</v>
+        <v>0.16615</v>
       </c>
     </row>
     <row r="170">
@@ -6328,7 +6328,7 @@
         </is>
       </c>
       <c r="K170">
-        <v>0.186198</v>
+        <v>0.187584</v>
       </c>
     </row>
     <row r="171">
@@ -6363,7 +6363,7 @@
         </is>
       </c>
       <c r="K171">
-        <v>0.200246</v>
+        <v>0.201704</v>
       </c>
     </row>
     <row r="172">
@@ -6398,7 +6398,7 @@
         </is>
       </c>
       <c r="K172">
-        <v>0.181764</v>
+        <v>0.183818</v>
       </c>
     </row>
     <row r="173">
@@ -6433,7 +6433,7 @@
         </is>
       </c>
       <c r="K173">
-        <v>0.140169</v>
+        <v>0.141062</v>
       </c>
     </row>
     <row r="174">
@@ -6468,7 +6468,7 @@
         </is>
       </c>
       <c r="K174">
-        <v>0.149561</v>
+        <v>0.149664</v>
       </c>
     </row>
     <row r="175">
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="K175">
-        <v>0.118485</v>
+        <v>0.118486</v>
       </c>
     </row>
     <row r="176">
@@ -6538,7 +6538,7 @@
         </is>
       </c>
       <c r="K176">
-        <v>0.14373</v>
+        <v>0.142438</v>
       </c>
     </row>
     <row r="177">
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="K177">
-        <v>0.147422</v>
+        <v>0.142915</v>
       </c>
     </row>
     <row r="178">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="K178">
-        <v>0.298596</v>
+        <v>0.297555</v>
       </c>
     </row>
     <row r="179">
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="K179">
-        <v>0.146895</v>
+        <v>0.148139</v>
       </c>
     </row>
     <row r="180">
@@ -6678,7 +6678,7 @@
         </is>
       </c>
       <c r="K180">
-        <v>0.139623</v>
+        <v>0.145498</v>
       </c>
     </row>
     <row r="181">
@@ -6713,7 +6713,7 @@
         </is>
       </c>
       <c r="K181">
-        <v>0.127505</v>
+        <v>0.140523</v>
       </c>
     </row>
     <row r="182">
@@ -6748,7 +6748,7 @@
         </is>
       </c>
       <c r="K182">
-        <v>0.150076</v>
+        <v>0.164834</v>
       </c>
     </row>
     <row r="183">
@@ -6783,7 +6783,7 @@
         </is>
       </c>
       <c r="K183">
-        <v>0.126842</v>
+        <v>0.167974</v>
       </c>
     </row>
     <row r="184">
@@ -6818,7 +6818,7 @@
         </is>
       </c>
       <c r="K184">
-        <v>0.146981</v>
+        <v>0.140737</v>
       </c>
     </row>
     <row r="185">
@@ -6853,7 +6853,7 @@
         </is>
       </c>
       <c r="K185">
-        <v>0.162436</v>
+        <v>0.155085</v>
       </c>
     </row>
     <row r="186">
@@ -6888,7 +6888,7 @@
         </is>
       </c>
       <c r="K186">
-        <v>0.207391</v>
+        <v>0.204437</v>
       </c>
     </row>
     <row r="187">
@@ -6923,7 +6923,7 @@
         </is>
       </c>
       <c r="K187">
-        <v>0.161501</v>
+        <v>0.197645</v>
       </c>
     </row>
     <row r="188">
@@ -6958,7 +6958,7 @@
         </is>
       </c>
       <c r="K188">
-        <v>0.151704</v>
+        <v>0.156608</v>
       </c>
     </row>
     <row r="189">
@@ -6993,7 +6993,7 @@
         </is>
       </c>
       <c r="K189">
-        <v>0.149747</v>
+        <v>0.153388</v>
       </c>
     </row>
     <row r="190">
@@ -7028,7 +7028,7 @@
         </is>
       </c>
       <c r="K190">
-        <v>0.137152</v>
+        <v>0.202567</v>
       </c>
     </row>
     <row r="191">
@@ -7063,7 +7063,7 @@
         </is>
       </c>
       <c r="K191">
-        <v>0.177165</v>
+        <v>0.17272</v>
       </c>
     </row>
     <row r="192">
@@ -7098,7 +7098,7 @@
         </is>
       </c>
       <c r="K192">
-        <v>0.132375</v>
+        <v>0.124289</v>
       </c>
     </row>
     <row r="193">
@@ -7133,7 +7133,7 @@
         </is>
       </c>
       <c r="K193">
-        <v>0.116352</v>
+        <v>0.116653</v>
       </c>
     </row>
     <row r="194">
@@ -7168,7 +7168,7 @@
         </is>
       </c>
       <c r="K194">
-        <v>0.117916</v>
+        <v>0.116456</v>
       </c>
     </row>
     <row r="195">
@@ -7203,7 +7203,7 @@
         </is>
       </c>
       <c r="K195">
-        <v>0.133021</v>
+        <v>0.130928</v>
       </c>
     </row>
     <row r="196">
@@ -7238,7 +7238,7 @@
         </is>
       </c>
       <c r="K196">
-        <v>0.122523</v>
+        <v>0.128764</v>
       </c>
     </row>
     <row r="197">
@@ -7273,7 +7273,7 @@
         </is>
       </c>
       <c r="K197">
-        <v>0.121973</v>
+        <v>0.122877</v>
       </c>
     </row>
     <row r="198">
@@ -7308,7 +7308,7 @@
         </is>
       </c>
       <c r="K198">
-        <v>0.121802</v>
+        <v>0.125339</v>
       </c>
     </row>
     <row r="199">
@@ -7343,7 +7343,7 @@
         </is>
       </c>
       <c r="K199">
-        <v>0.113449</v>
+        <v>0.118156</v>
       </c>
     </row>
     <row r="200">
@@ -7378,7 +7378,7 @@
         </is>
       </c>
       <c r="K200">
-        <v>0.133537</v>
+        <v>0.132246</v>
       </c>
     </row>
     <row r="201">
@@ -7413,7 +7413,7 @@
         </is>
       </c>
       <c r="K201">
-        <v>0.156179</v>
+        <v>0.153131</v>
       </c>
     </row>
     <row r="202">
@@ -7448,7 +7448,7 @@
         </is>
       </c>
       <c r="K202">
-        <v>0.13628</v>
+        <v>0.136225</v>
       </c>
     </row>
     <row r="203">
@@ -7483,7 +7483,7 @@
         </is>
       </c>
       <c r="K203">
-        <v>0.119696</v>
+        <v>0.123766</v>
       </c>
     </row>
     <row r="204">
@@ -7518,7 +7518,7 @@
         </is>
       </c>
       <c r="K204">
-        <v>0.140064</v>
+        <v>0.16169</v>
       </c>
     </row>
     <row r="205">
@@ -7553,7 +7553,7 @@
         </is>
       </c>
       <c r="K205">
-        <v>0.149336</v>
+        <v>0.152636</v>
       </c>
     </row>
     <row r="206">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="K206">
-        <v>0.123083</v>
+        <v>0.123599</v>
       </c>
     </row>
     <row r="207">
@@ -7623,7 +7623,7 @@
         </is>
       </c>
       <c r="K207">
-        <v>0.138084</v>
+        <v>0.162868</v>
       </c>
     </row>
     <row r="208">
@@ -7658,7 +7658,7 @@
         </is>
       </c>
       <c r="K208">
-        <v>0.129674</v>
+        <v>0.124603</v>
       </c>
     </row>
     <row r="209">
@@ -7693,7 +7693,7 @@
         </is>
       </c>
       <c r="K209">
-        <v>0.186237</v>
+        <v>0.1906</v>
       </c>
     </row>
     <row r="210">
@@ -7728,7 +7728,7 @@
         </is>
       </c>
       <c r="K210">
-        <v>0.222583</v>
+        <v>0.192704</v>
       </c>
     </row>
     <row r="211">
@@ -7763,7 +7763,7 @@
         </is>
       </c>
       <c r="K211">
-        <v>0.253121</v>
+        <v>0.200543</v>
       </c>
     </row>
     <row r="212">
@@ -7798,7 +7798,7 @@
         </is>
       </c>
       <c r="K212">
-        <v>0.140525</v>
+        <v>0.132995</v>
       </c>
     </row>
     <row r="213">
@@ -7833,7 +7833,7 @@
         </is>
       </c>
       <c r="K213">
-        <v>0.13514</v>
+        <v>0.136048</v>
       </c>
     </row>
     <row r="214">
@@ -7868,7 +7868,7 @@
         </is>
       </c>
       <c r="K214">
-        <v>0.212273</v>
+        <v>0.207534</v>
       </c>
     </row>
     <row r="215">
@@ -7903,7 +7903,7 @@
         </is>
       </c>
       <c r="K215">
-        <v>0.182323</v>
+        <v>0.427029</v>
       </c>
     </row>
     <row r="216">
@@ -7938,7 +7938,7 @@
         </is>
       </c>
       <c r="K216">
-        <v>0.20076</v>
+        <v>0.30245</v>
       </c>
     </row>
     <row r="217">
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="K217">
-        <v>0.113467</v>
+        <v>0.113931</v>
       </c>
     </row>
     <row r="218">
@@ -8008,7 +8008,7 @@
         </is>
       </c>
       <c r="K218">
-        <v>0.129595</v>
+        <v>0.131249</v>
       </c>
     </row>
     <row r="219">
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="K219">
-        <v>0.151243</v>
+        <v>0.150777</v>
       </c>
     </row>
     <row r="220">
@@ -8078,7 +8078,7 @@
         </is>
       </c>
       <c r="K220">
-        <v>0.132537</v>
+        <v>0.133699</v>
       </c>
     </row>
     <row r="221">
@@ -8113,7 +8113,7 @@
         </is>
       </c>
       <c r="K221">
-        <v>0.130364</v>
+        <v>0.129322</v>
       </c>
     </row>
     <row r="222">
@@ -8148,7 +8148,7 @@
         </is>
       </c>
       <c r="K222">
-        <v>0.133996</v>
+        <v>0.13844</v>
       </c>
     </row>
     <row r="223">
@@ -8183,7 +8183,7 @@
         </is>
       </c>
       <c r="K223">
-        <v>0.132627</v>
+        <v>0.134064</v>
       </c>
     </row>
     <row r="224">
@@ -8218,7 +8218,7 @@
         </is>
       </c>
       <c r="K224">
-        <v>0.170174</v>
+        <v>0.17671</v>
       </c>
     </row>
     <row r="225">
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="K225">
-        <v>0.143379</v>
+        <v>0.153053</v>
       </c>
     </row>
     <row r="226">
@@ -8288,7 +8288,7 @@
         </is>
       </c>
       <c r="K226">
-        <v>0.170123</v>
+        <v>0.175126</v>
       </c>
     </row>
     <row r="227">
@@ -8323,7 +8323,7 @@
         </is>
       </c>
       <c r="K227">
-        <v>0.194633</v>
+        <v>0.197314</v>
       </c>
     </row>
     <row r="228">
@@ -8358,7 +8358,7 @@
         </is>
       </c>
       <c r="K228">
-        <v>0.135315</v>
+        <v>0.140471</v>
       </c>
     </row>
     <row r="229">
@@ -8393,7 +8393,7 @@
         </is>
       </c>
       <c r="K229">
-        <v>0.17633</v>
+        <v>0.182215</v>
       </c>
     </row>
     <row r="230">
@@ -8428,7 +8428,7 @@
         </is>
       </c>
       <c r="K230">
-        <v>0.191803</v>
+        <v>0.194114</v>
       </c>
     </row>
     <row r="231">
@@ -8463,7 +8463,7 @@
         </is>
       </c>
       <c r="K231">
-        <v>0.174078</v>
+        <v>0.188634</v>
       </c>
     </row>
     <row r="232">
@@ -8498,7 +8498,7 @@
         </is>
       </c>
       <c r="K232">
-        <v>0.149931</v>
+        <v>0.146702</v>
       </c>
     </row>
     <row r="233">
@@ -8533,7 +8533,7 @@
         </is>
       </c>
       <c r="K233">
-        <v>0.153569</v>
+        <v>0.151142</v>
       </c>
     </row>
     <row r="234">
@@ -8568,7 +8568,7 @@
         </is>
       </c>
       <c r="K234">
-        <v>0.121588</v>
+        <v>0.121905</v>
       </c>
     </row>
     <row r="235">
@@ -8603,7 +8603,7 @@
         </is>
       </c>
       <c r="K235">
-        <v>0.179585</v>
+        <v>0.175412</v>
       </c>
     </row>
     <row r="236">
@@ -8638,7 +8638,7 @@
         </is>
       </c>
       <c r="K236">
-        <v>0.14437</v>
+        <v>0.146228</v>
       </c>
     </row>
     <row r="237">
@@ -8673,7 +8673,7 @@
         </is>
       </c>
       <c r="K237">
-        <v>0.148639</v>
+        <v>0.148391</v>
       </c>
     </row>
     <row r="238">
@@ -8708,7 +8708,7 @@
         </is>
       </c>
       <c r="K238">
-        <v>0.136538</v>
+        <v>0.136522</v>
       </c>
     </row>
   </sheetData>
